--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2915-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2915-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF7DD199-32C7-4499-8F79-B5153725B91F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{27D5E94C-AD79-4FDE-B7CD-7A7834887484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{098A6423-6050-4759-81A4-1F052349A2FB}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{506DF2AF-7FDB-424A-8BC8-8D8DE07370C5}"/>
   </bookViews>
   <sheets>
     <sheet name="2915-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1529,27 +1529,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C8A1436-5D1B-480F-963B-7F44C67BACA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51A4698D-653E-42D1-A980-007E38700AED}">
   <dimension ref="A1:X48"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1583,7 +1582,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1619,7 +1618,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1671,7 +1670,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1739,7 +1738,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2024</v>
       </c>
@@ -1811,7 +1810,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="38">
         <v>2023</v>
       </c>
@@ -1883,7 +1882,7 @@
         <v>4.34</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="36">
         <v>2022</v>
       </c>
@@ -1955,7 +1954,7 @@
         <v>3.76</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="38">
         <v>2021</v>
       </c>
@@ -2027,7 +2026,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="40">
         <v>2020</v>
       </c>
@@ -2099,7 +2098,7 @@
         <v>7.34</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="42"/>
       <c r="B10" s="43"/>
       <c r="C10" s="18" t="s">
@@ -2127,7 +2126,7 @@
       <c r="W10" s="49"/>
       <c r="X10" s="45"/>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2019</v>
       </c>
@@ -2199,7 +2198,7 @@
         <v>8.4700000000000006</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2018</v>
       </c>
@@ -2271,7 +2270,7 @@
         <v>8.9600000000000009</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2017</v>
       </c>
@@ -2343,7 +2342,7 @@
         <v>8.6199999999999992</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2016</v>
       </c>
@@ -2415,7 +2414,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2015</v>
       </c>
@@ -2487,7 +2486,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2014</v>
       </c>
@@ -2559,7 +2558,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2013</v>
       </c>
@@ -2631,7 +2630,7 @@
         <v>8.31</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2012</v>
       </c>
@@ -2703,7 +2702,7 @@
         <v>4.9400000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2011</v>
       </c>
@@ -2775,7 +2774,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2010</v>
       </c>
@@ -2847,7 +2846,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2009</v>
       </c>
@@ -2919,7 +2918,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2008</v>
       </c>
@@ -2991,7 +2990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2007</v>
       </c>
@@ -3063,7 +3062,7 @@
         <v>8.11</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2006</v>
       </c>
@@ -3135,7 +3134,7 @@
         <v>5.64</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2005</v>
       </c>
@@ -3207,7 +3206,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2004</v>
       </c>
@@ -3279,7 +3278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2003</v>
       </c>
@@ -3351,7 +3350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2002</v>
       </c>
@@ -3423,7 +3422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2001</v>
       </c>
@@ -3495,7 +3494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>2000</v>
       </c>
@@ -3567,7 +3566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>1999</v>
       </c>
@@ -3639,7 +3638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="40">
         <v>1998</v>
       </c>
@@ -3711,7 +3710,7 @@
         <v>7.41</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="42"/>
       <c r="B33" s="43"/>
       <c r="C33" s="18" t="s">
@@ -3739,7 +3738,7 @@
       <c r="W33" s="49"/>
       <c r="X33" s="45"/>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="38">
         <v>1997</v>
       </c>
@@ -3811,7 +3810,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="36">
         <v>1996</v>
       </c>
@@ -3883,7 +3882,7 @@
         <v>9.6199999999999992</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="38">
         <v>1995</v>
       </c>
@@ -3955,7 +3954,7 @@
         <v>4.3499999999999996</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="36">
         <v>1994</v>
       </c>
@@ -4027,7 +4026,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="38">
         <v>1993</v>
       </c>
@@ -4099,7 +4098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="36">
         <v>1992</v>
       </c>
@@ -4171,7 +4170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="38">
         <v>1991</v>
       </c>
@@ -4243,7 +4242,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="36">
         <v>1990</v>
       </c>
@@ -4315,7 +4314,7 @@
         <v>3.68</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="38">
         <v>1989</v>
       </c>
@@ -4387,7 +4386,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="36">
         <v>1988</v>
       </c>
@@ -4459,7 +4458,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="38">
         <v>1987</v>
       </c>
@@ -4531,7 +4530,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="36">
         <v>1986</v>
       </c>
@@ -4603,7 +4602,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="38">
         <v>1984</v>
       </c>
@@ -4675,7 +4674,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="36">
         <v>1983</v>
       </c>
@@ -4747,7 +4746,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="38" t="s">
         <v>56</v>
       </c>
